--- a/Build/TICKET-101_Update.xlsx
+++ b/Build/TICKET-101_Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Praveen Kumar\Desktop\Git_Geeks\Build\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C9F47C-8036-433B-9250-2E1F454C1B68}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{252CFAE8-1838-4619-9CAA-CB3079E6B9FB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7635" xr2:uid="{9AE947FB-0D16-4716-A8D3-038FFDBF1919}"/>
   </bookViews>
@@ -454,6 +454,7 @@
     <col min="2" max="2" width="22.73046875" customWidth="1"/>
     <col min="4" max="4" width="13.33203125" customWidth="1"/>
     <col min="5" max="5" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="11.86328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
